--- a/data/assessment/global_assessment_2025.xlsx
+++ b/data/assessment/global_assessment_2025.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4515" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4529" uniqueCount="422">
   <si>
     <t xml:space="preserve">Country Data for the 2025 Global Assessment on Environmental-Economic Accounting and Supporting Statistics</t>
   </si>
@@ -2534,9 +2534,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1505160</xdr:colOff>
+      <xdr:colOff>1504800</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>610560</xdr:rowOff>
+      <xdr:rowOff>610200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2551,7 +2551,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="200160" y="53280"/>
-          <a:ext cx="1607400" cy="747720"/>
+          <a:ext cx="1607040" cy="747360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2573,9 +2573,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1270800</xdr:colOff>
+      <xdr:colOff>1270440</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>20520</xdr:rowOff>
+      <xdr:rowOff>20160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2589,7 +2589,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="313920" y="866880"/>
-          <a:ext cx="1259280" cy="572760"/>
+          <a:ext cx="1258920" cy="572400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2611,9 +2611,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>21600</xdr:colOff>
+      <xdr:colOff>21240</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>89640</xdr:rowOff>
+      <xdr:rowOff>89280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2625,7 +2625,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10116360" y="4410360"/>
-          <a:ext cx="1080720" cy="307080"/>
+          <a:ext cx="1080360" cy="306720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2666,7 +2666,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>939600</xdr:colOff>
+      <xdr:colOff>939240</xdr:colOff>
       <xdr:row>77</xdr:row>
       <xdr:rowOff>133560</xdr:rowOff>
     </xdr:to>
@@ -2680,7 +2680,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13962960" y="2781000"/>
-          <a:ext cx="874800" cy="360"/>
+          <a:ext cx="874440" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2734,73 +2734,7 @@
               <a:uFillTx/>
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
-            <a:t>https://</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Aptos Narrow"/>
-            </a:rPr>
-            <a:t>www.statist</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Aptos Narrow"/>
-            </a:rPr>
-            <a:t>ik.at/en/</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Aptos Narrow"/>
-            </a:rPr>
-            <a:t>statistics/</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Aptos Narrow"/>
-            </a:rPr>
-            <a:t>energy-and-</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Aptos Narrow"/>
-            </a:rPr>
-            <a:t>environmen</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Aptos Narrow"/>
-            </a:rPr>
-            <a:t>t</a:t>
+            <a:t>https://www.statistik.at/en/statistics/energy-and-environment</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-001" sz="1100" b="0" u="none" strike="noStrike">
@@ -2832,7 +2766,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1230480</xdr:colOff>
+      <xdr:colOff>1230120</xdr:colOff>
       <xdr:row>139</xdr:row>
       <xdr:rowOff>106920</xdr:rowOff>
     </xdr:to>
@@ -2846,7 +2780,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14305680" y="4849920"/>
-          <a:ext cx="822960" cy="360"/>
+          <a:ext cx="822600" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2882,9 +2816,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>817560</xdr:colOff>
+      <xdr:colOff>817200</xdr:colOff>
       <xdr:row>145</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>112320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2896,7 +2830,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13913280" y="5996880"/>
-          <a:ext cx="802440" cy="2160"/>
+          <a:ext cx="802080" cy="1800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2932,7 +2866,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>973800</xdr:colOff>
+      <xdr:colOff>973440</xdr:colOff>
       <xdr:row>145</xdr:row>
       <xdr:rowOff>189360</xdr:rowOff>
     </xdr:to>
@@ -2946,7 +2880,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14126760" y="6075360"/>
-          <a:ext cx="745200" cy="360"/>
+          <a:ext cx="744840" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2982,7 +2916,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>872640</xdr:colOff>
+      <xdr:colOff>872280</xdr:colOff>
       <xdr:row>77</xdr:row>
       <xdr:rowOff>118440</xdr:rowOff>
     </xdr:to>
@@ -2996,7 +2930,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13917240" y="2765880"/>
-          <a:ext cx="853560" cy="360"/>
+          <a:ext cx="853200" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3050,73 +2984,7 @@
               <a:uFillTx/>
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
-            <a:t>https://</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Aptos Narrow"/>
-            </a:rPr>
-            <a:t>www.statist</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Aptos Narrow"/>
-            </a:rPr>
-            <a:t>ik.at/en/</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Aptos Narrow"/>
-            </a:rPr>
-            <a:t>statistics/</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Aptos Narrow"/>
-            </a:rPr>
-            <a:t>energy-and-</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Aptos Narrow"/>
-            </a:rPr>
-            <a:t>environmen</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Aptos Narrow"/>
-            </a:rPr>
-            <a:t>t</a:t>
+            <a:t>https://www.statistik.at/en/statistics/energy-and-environment</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-001" sz="1100" b="0" u="none" strike="noStrike">
@@ -3148,9 +3016,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>892080</xdr:colOff>
+      <xdr:colOff>891720</xdr:colOff>
       <xdr:row>160</xdr:row>
-      <xdr:rowOff>143280</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3162,7 +3030,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13905720" y="8812800"/>
-          <a:ext cx="884520" cy="74520"/>
+          <a:ext cx="884160" cy="74160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3198,9 +3066,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1257840</xdr:colOff>
+      <xdr:colOff>1257480</xdr:colOff>
       <xdr:row>160</xdr:row>
-      <xdr:rowOff>143280</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3212,7 +3080,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14271480" y="8812800"/>
-          <a:ext cx="884520" cy="74520"/>
+          <a:ext cx="884160" cy="74160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3248,9 +3116,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>907560</xdr:colOff>
+      <xdr:colOff>907200</xdr:colOff>
       <xdr:row>174</xdr:row>
-      <xdr:rowOff>143280</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3262,7 +3130,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13921200" y="11479680"/>
-          <a:ext cx="884520" cy="74520"/>
+          <a:ext cx="884160" cy="74160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3298,9 +3166,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1311120</xdr:colOff>
+      <xdr:colOff>1310760</xdr:colOff>
       <xdr:row>174</xdr:row>
-      <xdr:rowOff>143280</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3312,7 +3180,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14324760" y="11479680"/>
-          <a:ext cx="884520" cy="74520"/>
+          <a:ext cx="884160" cy="74160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3348,9 +3216,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>680400</xdr:colOff>
+      <xdr:colOff>680040</xdr:colOff>
       <xdr:row>177</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>112320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3362,7 +3230,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13921200" y="12051360"/>
-          <a:ext cx="657360" cy="43920"/>
+          <a:ext cx="657000" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3398,9 +3266,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1011960</xdr:colOff>
+      <xdr:colOff>1011600</xdr:colOff>
       <xdr:row>177</xdr:row>
-      <xdr:rowOff>135360</xdr:rowOff>
+      <xdr:rowOff>135000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3412,7 +3280,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14667840" y="12074040"/>
-          <a:ext cx="242280" cy="43920"/>
+          <a:ext cx="241920" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3448,9 +3316,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1053720</xdr:colOff>
+      <xdr:colOff>1053360</xdr:colOff>
       <xdr:row>177</xdr:row>
-      <xdr:rowOff>135360</xdr:rowOff>
+      <xdr:rowOff>135000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3462,7 +3330,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14294520" y="12074040"/>
-          <a:ext cx="657360" cy="43920"/>
+          <a:ext cx="657000" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3498,7 +3366,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>672480</xdr:colOff>
+      <xdr:colOff>672120</xdr:colOff>
       <xdr:row>179</xdr:row>
       <xdr:rowOff>106920</xdr:rowOff>
     </xdr:to>
@@ -3512,7 +3380,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13913280" y="12470040"/>
-          <a:ext cx="657360" cy="360"/>
+          <a:ext cx="657000" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3548,7 +3416,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1083960</xdr:colOff>
+      <xdr:colOff>1083600</xdr:colOff>
       <xdr:row>179</xdr:row>
       <xdr:rowOff>106920</xdr:rowOff>
     </xdr:to>
@@ -3562,7 +3430,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14324760" y="12470040"/>
-          <a:ext cx="657360" cy="360"/>
+          <a:ext cx="657000" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3598,9 +3466,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1131480</xdr:colOff>
+      <xdr:colOff>1131120</xdr:colOff>
       <xdr:row>250</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>112320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3612,7 +3480,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14309640" y="25934760"/>
-          <a:ext cx="720000" cy="66960"/>
+          <a:ext cx="719640" cy="66600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3648,9 +3516,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>743040</xdr:colOff>
+      <xdr:colOff>742680</xdr:colOff>
       <xdr:row>250</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>112320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3662,7 +3530,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13921200" y="25934760"/>
-          <a:ext cx="720000" cy="66960"/>
+          <a:ext cx="719640" cy="66600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3698,9 +3566,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>717120</xdr:colOff>
+      <xdr:colOff>716760</xdr:colOff>
       <xdr:row>183</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>112320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3712,7 +3580,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13936320" y="13171320"/>
-          <a:ext cx="678960" cy="66960"/>
+          <a:ext cx="678600" cy="66600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3748,9 +3616,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1059840</xdr:colOff>
+      <xdr:colOff>1059480</xdr:colOff>
       <xdr:row>183</xdr:row>
-      <xdr:rowOff>97560</xdr:rowOff>
+      <xdr:rowOff>97200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3762,7 +3630,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14279040" y="13156200"/>
-          <a:ext cx="678960" cy="66960"/>
+          <a:ext cx="678600" cy="66600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3798,9 +3666,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>702000</xdr:colOff>
+      <xdr:colOff>701640</xdr:colOff>
       <xdr:row>188</xdr:row>
-      <xdr:rowOff>105120</xdr:rowOff>
+      <xdr:rowOff>104760</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3812,7 +3680,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13921200" y="14115960"/>
-          <a:ext cx="678960" cy="66960"/>
+          <a:ext cx="678600" cy="66600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3848,9 +3716,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1113120</xdr:colOff>
+      <xdr:colOff>1112760</xdr:colOff>
       <xdr:row>188</xdr:row>
-      <xdr:rowOff>97560</xdr:rowOff>
+      <xdr:rowOff>97200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3862,7 +3730,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14332680" y="14108400"/>
-          <a:ext cx="678600" cy="66960"/>
+          <a:ext cx="678240" cy="66600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3898,7 +3766,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1065240</xdr:colOff>
+      <xdr:colOff>1064880</xdr:colOff>
       <xdr:row>188</xdr:row>
       <xdr:rowOff>84240</xdr:rowOff>
     </xdr:to>
@@ -3912,7 +3780,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14713560" y="14161680"/>
-          <a:ext cx="249840" cy="360"/>
+          <a:ext cx="249480" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3948,9 +3816,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>601200</xdr:colOff>
+      <xdr:colOff>600840</xdr:colOff>
       <xdr:row>249</xdr:row>
-      <xdr:rowOff>122040</xdr:rowOff>
+      <xdr:rowOff>121680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3962,7 +3830,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13937400" y="25757280"/>
-          <a:ext cx="561960" cy="63360"/>
+          <a:ext cx="561600" cy="63000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3998,9 +3866,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>929160</xdr:colOff>
+      <xdr:colOff>928800</xdr:colOff>
       <xdr:row>249</xdr:row>
-      <xdr:rowOff>131040</xdr:rowOff>
+      <xdr:rowOff>130680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4012,7 +3880,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14265360" y="25766280"/>
-          <a:ext cx="561960" cy="63360"/>
+          <a:ext cx="561600" cy="63000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4048,9 +3916,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>742320</xdr:colOff>
+      <xdr:colOff>741960</xdr:colOff>
       <xdr:row>239</xdr:row>
-      <xdr:rowOff>96120</xdr:rowOff>
+      <xdr:rowOff>95760</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4062,7 +3930,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13937400" y="23845680"/>
-          <a:ext cx="703080" cy="43920"/>
+          <a:ext cx="702720" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4098,9 +3966,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1122480</xdr:colOff>
+      <xdr:colOff>1122120</xdr:colOff>
       <xdr:row>239</xdr:row>
-      <xdr:rowOff>105120</xdr:rowOff>
+      <xdr:rowOff>104760</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4112,7 +3980,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14317560" y="23854680"/>
-          <a:ext cx="703080" cy="43920"/>
+          <a:ext cx="702720" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4148,7 +4016,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1052280</xdr:colOff>
+      <xdr:colOff>1051920</xdr:colOff>
       <xdr:row>239</xdr:row>
       <xdr:rowOff>87480</xdr:rowOff>
     </xdr:to>
@@ -4162,7 +4030,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14691600" y="23880600"/>
-          <a:ext cx="258840" cy="360"/>
+          <a:ext cx="258480" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4198,9 +4066,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>722880</xdr:colOff>
+      <xdr:colOff>722520</xdr:colOff>
       <xdr:row>120</xdr:row>
-      <xdr:rowOff>109080</xdr:rowOff>
+      <xdr:rowOff>108720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4212,7 +4080,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13917600" y="4033800"/>
-          <a:ext cx="703440" cy="56880"/>
+          <a:ext cx="703080" cy="56520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4248,9 +4116,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1070640</xdr:colOff>
+      <xdr:colOff>1070280</xdr:colOff>
       <xdr:row>120</xdr:row>
-      <xdr:rowOff>105120</xdr:rowOff>
+      <xdr:rowOff>104760</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4262,7 +4130,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14265360" y="4042800"/>
-          <a:ext cx="703440" cy="43920"/>
+          <a:ext cx="703080" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4298,9 +4166,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>788040</xdr:colOff>
+      <xdr:colOff>787680</xdr:colOff>
       <xdr:row>237</xdr:row>
-      <xdr:rowOff>128520</xdr:rowOff>
+      <xdr:rowOff>128160</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4312,7 +4180,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13930560" y="23497200"/>
-          <a:ext cx="755640" cy="43920"/>
+          <a:ext cx="755280" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4348,9 +4216,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1232280</xdr:colOff>
+      <xdr:colOff>1231920</xdr:colOff>
       <xdr:row>237</xdr:row>
-      <xdr:rowOff>109440</xdr:rowOff>
+      <xdr:rowOff>109080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4362,7 +4230,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14311080" y="23520240"/>
-          <a:ext cx="819360" cy="1800"/>
+          <a:ext cx="819000" cy="1440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4398,9 +4266,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>923040</xdr:colOff>
+      <xdr:colOff>922680</xdr:colOff>
       <xdr:row>232</xdr:row>
-      <xdr:rowOff>109080</xdr:rowOff>
+      <xdr:rowOff>108720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4412,7 +4280,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13924080" y="22525200"/>
-          <a:ext cx="897120" cy="43920"/>
+          <a:ext cx="896760" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4448,9 +4316,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1342440</xdr:colOff>
+      <xdr:colOff>1342080</xdr:colOff>
       <xdr:row>232</xdr:row>
-      <xdr:rowOff>105120</xdr:rowOff>
+      <xdr:rowOff>104760</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4460,7 +4328,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14343480" y="22521240"/>
-          <a:ext cx="897120" cy="43920"/>
+          <a:ext cx="896760" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4496,9 +4364,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1202400</xdr:colOff>
+      <xdr:colOff>1202040</xdr:colOff>
       <xdr:row>232</xdr:row>
-      <xdr:rowOff>101160</xdr:rowOff>
+      <xdr:rowOff>100800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4510,7 +4378,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14769720" y="22517280"/>
-          <a:ext cx="330840" cy="43920"/>
+          <a:ext cx="330480" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4546,9 +4414,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>731160</xdr:colOff>
+      <xdr:colOff>730800</xdr:colOff>
       <xdr:row>230</xdr:row>
-      <xdr:rowOff>128520</xdr:rowOff>
+      <xdr:rowOff>128160</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4560,7 +4428,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13943880" y="22156920"/>
-          <a:ext cx="685440" cy="50400"/>
+          <a:ext cx="685080" cy="50040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4596,9 +4464,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1098720</xdr:colOff>
+      <xdr:colOff>1098360</xdr:colOff>
       <xdr:row>230</xdr:row>
-      <xdr:rowOff>124560</xdr:rowOff>
+      <xdr:rowOff>124200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4610,7 +4478,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14311080" y="22152960"/>
-          <a:ext cx="685800" cy="50400"/>
+          <a:ext cx="685440" cy="50040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4646,9 +4514,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1039680</xdr:colOff>
+      <xdr:colOff>1039320</xdr:colOff>
       <xdr:row>230</xdr:row>
-      <xdr:rowOff>120600</xdr:rowOff>
+      <xdr:rowOff>120240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4660,7 +4528,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14684760" y="22149000"/>
-          <a:ext cx="253080" cy="50400"/>
+          <a:ext cx="252720" cy="50040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4696,9 +4564,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>673200</xdr:colOff>
+      <xdr:colOff>672840</xdr:colOff>
       <xdr:row>223</xdr:row>
-      <xdr:rowOff>109080</xdr:rowOff>
+      <xdr:rowOff>108720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4710,7 +4578,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13956840" y="20810520"/>
-          <a:ext cx="614520" cy="43920"/>
+          <a:ext cx="614160" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4746,9 +4614,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1040400</xdr:colOff>
+      <xdr:colOff>1040040</xdr:colOff>
       <xdr:row>223</xdr:row>
-      <xdr:rowOff>111600</xdr:rowOff>
+      <xdr:rowOff>111240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4760,7 +4628,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14324040" y="20813040"/>
-          <a:ext cx="614520" cy="43920"/>
+          <a:ext cx="614160" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4796,9 +4664,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>746640</xdr:colOff>
+      <xdr:colOff>746280</xdr:colOff>
       <xdr:row>220</xdr:row>
-      <xdr:rowOff>89640</xdr:rowOff>
+      <xdr:rowOff>89280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4810,7 +4678,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13924080" y="20213280"/>
-          <a:ext cx="720720" cy="50400"/>
+          <a:ext cx="720360" cy="50040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4846,7 +4714,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1140120</xdr:colOff>
+      <xdr:colOff>1139760</xdr:colOff>
       <xdr:row>220</xdr:row>
       <xdr:rowOff>90360</xdr:rowOff>
     </xdr:to>
@@ -4860,7 +4728,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14317560" y="20264040"/>
-          <a:ext cx="720720" cy="360"/>
+          <a:ext cx="720360" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4896,9 +4764,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>695160</xdr:colOff>
+      <xdr:colOff>694800</xdr:colOff>
       <xdr:row>212</xdr:row>
-      <xdr:rowOff>83160</xdr:rowOff>
+      <xdr:rowOff>82800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4910,7 +4778,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13943880" y="18689040"/>
-          <a:ext cx="649440" cy="43920"/>
+          <a:ext cx="649080" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4946,7 +4814,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1036080</xdr:colOff>
+      <xdr:colOff>1035720</xdr:colOff>
       <xdr:row>212</xdr:row>
       <xdr:rowOff>77400</xdr:rowOff>
     </xdr:to>
@@ -4960,7 +4828,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14695200" y="18726840"/>
-          <a:ext cx="239040" cy="360"/>
+          <a:ext cx="238680" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4996,7 +4864,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1177560</xdr:colOff>
+      <xdr:colOff>1177200</xdr:colOff>
       <xdr:row>212</xdr:row>
       <xdr:rowOff>63720</xdr:rowOff>
     </xdr:to>
@@ -5010,7 +4878,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14249880" y="18713160"/>
-          <a:ext cx="825840" cy="360"/>
+          <a:ext cx="825480" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5046,7 +4914,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2310480</xdr:colOff>
+      <xdr:colOff>2310120</xdr:colOff>
       <xdr:row>212</xdr:row>
       <xdr:rowOff>88920</xdr:rowOff>
     </xdr:to>
@@ -5060,7 +4928,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="15910560" y="18738360"/>
-          <a:ext cx="298080" cy="360"/>
+          <a:ext cx="297720" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5096,7 +4964,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1870200</xdr:colOff>
+      <xdr:colOff>1869840</xdr:colOff>
       <xdr:row>212</xdr:row>
       <xdr:rowOff>91800</xdr:rowOff>
     </xdr:to>
@@ -5108,7 +4976,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="15470280" y="18741240"/>
-          <a:ext cx="298080" cy="360"/>
+          <a:ext cx="297720" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5144,9 +5012,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1442520</xdr:colOff>
+      <xdr:colOff>1442160</xdr:colOff>
       <xdr:row>212</xdr:row>
-      <xdr:rowOff>92160</xdr:rowOff>
+      <xdr:rowOff>91800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5158,7 +5026,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="15042960" y="18738360"/>
-          <a:ext cx="297720" cy="3600"/>
+          <a:ext cx="297360" cy="3240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5194,9 +5062,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>731160</xdr:colOff>
+      <xdr:colOff>730800</xdr:colOff>
       <xdr:row>211</xdr:row>
-      <xdr:rowOff>109080</xdr:rowOff>
+      <xdr:rowOff>108720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5208,7 +5076,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13943880" y="18524520"/>
-          <a:ext cx="685440" cy="43920"/>
+          <a:ext cx="685080" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5244,7 +5112,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1062360</xdr:colOff>
+      <xdr:colOff>1062000</xdr:colOff>
       <xdr:row>211</xdr:row>
       <xdr:rowOff>96840</xdr:rowOff>
     </xdr:to>
@@ -5258,7 +5126,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14708520" y="18555840"/>
-          <a:ext cx="252000" cy="360"/>
+          <a:ext cx="251640" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5294,9 +5162,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1050480</xdr:colOff>
+      <xdr:colOff>1050120</xdr:colOff>
       <xdr:row>211</xdr:row>
-      <xdr:rowOff>126000</xdr:rowOff>
+      <xdr:rowOff>125640</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5308,7 +5176,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14262840" y="18541440"/>
-          <a:ext cx="685800" cy="43920"/>
+          <a:ext cx="685440" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5344,9 +5212,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>729000</xdr:colOff>
+      <xdr:colOff>728640</xdr:colOff>
       <xdr:row>201</xdr:row>
-      <xdr:rowOff>115560</xdr:rowOff>
+      <xdr:rowOff>115200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5358,7 +5226,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13924080" y="16626240"/>
-          <a:ext cx="703080" cy="43920"/>
+          <a:ext cx="702720" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5394,9 +5262,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1096560</xdr:colOff>
+      <xdr:colOff>1096200</xdr:colOff>
       <xdr:row>201</xdr:row>
-      <xdr:rowOff>118080</xdr:rowOff>
+      <xdr:rowOff>117720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5408,7 +5276,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14291640" y="16628760"/>
-          <a:ext cx="703080" cy="43920"/>
+          <a:ext cx="702720" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5444,9 +5312,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>987840</xdr:colOff>
+      <xdr:colOff>987480</xdr:colOff>
       <xdr:row>72</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:rowOff>165960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5458,7 +5326,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13940280" y="2527560"/>
-          <a:ext cx="945720" cy="96120"/>
+          <a:ext cx="945360" cy="95760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5494,9 +5362,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1432080</xdr:colOff>
+      <xdr:colOff>1431720</xdr:colOff>
       <xdr:row>72</xdr:row>
-      <xdr:rowOff>152280</xdr:rowOff>
+      <xdr:rowOff>151920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5508,7 +5376,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14346360" y="2527560"/>
-          <a:ext cx="983880" cy="82080"/>
+          <a:ext cx="983520" cy="81720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5544,9 +5412,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>817560</xdr:colOff>
+      <xdr:colOff>817200</xdr:colOff>
       <xdr:row>150</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>112320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5558,7 +5426,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13913280" y="6949440"/>
-          <a:ext cx="802440" cy="2160"/>
+          <a:ext cx="802080" cy="1800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5594,7 +5462,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>973800</xdr:colOff>
+      <xdr:colOff>973440</xdr:colOff>
       <xdr:row>150</xdr:row>
       <xdr:rowOff>189360</xdr:rowOff>
     </xdr:to>
@@ -5608,7 +5476,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14126760" y="7027920"/>
-          <a:ext cx="745200" cy="360"/>
+          <a:ext cx="744840" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5644,9 +5512,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>817560</xdr:colOff>
+      <xdr:colOff>817200</xdr:colOff>
       <xdr:row>156</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>112320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5658,7 +5526,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13913280" y="8092440"/>
-          <a:ext cx="802440" cy="2160"/>
+          <a:ext cx="802080" cy="1800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5694,7 +5562,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>973800</xdr:colOff>
+      <xdr:colOff>973440</xdr:colOff>
       <xdr:row>156</xdr:row>
       <xdr:rowOff>189360</xdr:rowOff>
     </xdr:to>
@@ -5708,7 +5576,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14126760" y="8170920"/>
-          <a:ext cx="745200" cy="360"/>
+          <a:ext cx="744840" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5744,9 +5612,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>817560</xdr:colOff>
+      <xdr:colOff>817200</xdr:colOff>
       <xdr:row>168</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>112320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5758,7 +5626,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13913280" y="10378440"/>
-          <a:ext cx="802440" cy="2160"/>
+          <a:ext cx="802080" cy="1800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5794,7 +5662,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>973800</xdr:colOff>
+      <xdr:colOff>973440</xdr:colOff>
       <xdr:row>168</xdr:row>
       <xdr:rowOff>189360</xdr:rowOff>
     </xdr:to>
@@ -5808,7 +5676,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14126760" y="10456920"/>
-          <a:ext cx="745200" cy="360"/>
+          <a:ext cx="744840" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5844,9 +5712,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>817560</xdr:colOff>
+      <xdr:colOff>817200</xdr:colOff>
       <xdr:row>165</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>112320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5858,7 +5726,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13913280" y="9807120"/>
-          <a:ext cx="802440" cy="2160"/>
+          <a:ext cx="802080" cy="1800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5894,7 +5762,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>973800</xdr:colOff>
+      <xdr:colOff>973440</xdr:colOff>
       <xdr:row>165</xdr:row>
       <xdr:rowOff>189360</xdr:rowOff>
     </xdr:to>
@@ -5908,7 +5776,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14126760" y="9885600"/>
-          <a:ext cx="745200" cy="360"/>
+          <a:ext cx="744840" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5944,9 +5812,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1058760</xdr:colOff>
+      <xdr:colOff>1058400</xdr:colOff>
       <xdr:row>145</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:rowOff>165960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5958,7 +5826,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13898160" y="5956560"/>
-          <a:ext cx="1058760" cy="96120"/>
+          <a:ext cx="1058400" cy="95760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5994,9 +5862,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1491840</xdr:colOff>
+      <xdr:colOff>1491480</xdr:colOff>
       <xdr:row>145</xdr:row>
-      <xdr:rowOff>164520</xdr:rowOff>
+      <xdr:rowOff>164160</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6008,7 +5876,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14330880" y="5954760"/>
-          <a:ext cx="1059120" cy="96120"/>
+          <a:ext cx="1058760" cy="95760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6044,9 +5912,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1110960</xdr:colOff>
+      <xdr:colOff>1110600</xdr:colOff>
       <xdr:row>150</xdr:row>
-      <xdr:rowOff>138240</xdr:rowOff>
+      <xdr:rowOff>137880</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6058,7 +5926,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13912200" y="6895080"/>
-          <a:ext cx="1096920" cy="82080"/>
+          <a:ext cx="1096560" cy="81720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6094,9 +5962,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1543320</xdr:colOff>
+      <xdr:colOff>1542960</xdr:colOff>
       <xdr:row>150</xdr:row>
-      <xdr:rowOff>150480</xdr:rowOff>
+      <xdr:rowOff>150120</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6108,7 +5976,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14344560" y="6907320"/>
-          <a:ext cx="1096920" cy="82080"/>
+          <a:ext cx="1096560" cy="81720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6144,9 +6012,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>950040</xdr:colOff>
+      <xdr:colOff>949680</xdr:colOff>
       <xdr:row>156</xdr:row>
-      <xdr:rowOff>138600</xdr:rowOff>
+      <xdr:rowOff>138240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6158,7 +6026,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13940280" y="8052120"/>
-          <a:ext cx="907920" cy="68400"/>
+          <a:ext cx="907560" cy="68040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6194,9 +6062,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1396440</xdr:colOff>
+      <xdr:colOff>1396080</xdr:colOff>
       <xdr:row>156</xdr:row>
-      <xdr:rowOff>136800</xdr:rowOff>
+      <xdr:rowOff>136440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6208,7 +6076,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14386680" y="8050320"/>
-          <a:ext cx="907920" cy="68400"/>
+          <a:ext cx="907560" cy="68040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6244,9 +6112,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>946440</xdr:colOff>
+      <xdr:colOff>946080</xdr:colOff>
       <xdr:row>165</xdr:row>
-      <xdr:rowOff>149040</xdr:rowOff>
+      <xdr:rowOff>148680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6258,7 +6126,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13936680" y="9777240"/>
-          <a:ext cx="907920" cy="68400"/>
+          <a:ext cx="907560" cy="68040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6294,9 +6162,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1393200</xdr:colOff>
+      <xdr:colOff>1392840</xdr:colOff>
       <xdr:row>165</xdr:row>
-      <xdr:rowOff>161280</xdr:rowOff>
+      <xdr:rowOff>160920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6308,7 +6176,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14383440" y="9789480"/>
-          <a:ext cx="907920" cy="68400"/>
+          <a:ext cx="907560" cy="68040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6344,9 +6212,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1237320</xdr:colOff>
+      <xdr:colOff>1236960</xdr:colOff>
       <xdr:row>165</xdr:row>
-      <xdr:rowOff>145800</xdr:rowOff>
+      <xdr:rowOff>145440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6358,7 +6226,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14801760" y="9774000"/>
-          <a:ext cx="333720" cy="68400"/>
+          <a:ext cx="333360" cy="68040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6394,9 +6262,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>964080</xdr:colOff>
+      <xdr:colOff>963720</xdr:colOff>
       <xdr:row>168</xdr:row>
-      <xdr:rowOff>152280</xdr:rowOff>
+      <xdr:rowOff>151920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6408,7 +6276,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13954320" y="10351800"/>
-          <a:ext cx="907920" cy="68400"/>
+          <a:ext cx="907560" cy="68040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6444,9 +6312,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1382400</xdr:colOff>
+      <xdr:colOff>1382040</xdr:colOff>
       <xdr:row>168</xdr:row>
-      <xdr:rowOff>136800</xdr:rowOff>
+      <xdr:rowOff>136440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6458,7 +6326,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14372640" y="10336320"/>
-          <a:ext cx="907920" cy="68400"/>
+          <a:ext cx="907560" cy="68040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6499,7 +6367,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>939600</xdr:colOff>
+      <xdr:colOff>939240</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>133560</xdr:rowOff>
     </xdr:to>
@@ -6511,7 +6379,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13962960" y="2600280"/>
-          <a:ext cx="874800" cy="360"/>
+          <a:ext cx="874440" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6597,7 +6465,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1230480</xdr:colOff>
+      <xdr:colOff>1230120</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>106920</xdr:rowOff>
     </xdr:to>
@@ -6609,7 +6477,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14305680" y="4669200"/>
-          <a:ext cx="822960" cy="360"/>
+          <a:ext cx="822600" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6645,9 +6513,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>817560</xdr:colOff>
+      <xdr:colOff>817200</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>112320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6657,7 +6525,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13913280" y="5816160"/>
-          <a:ext cx="802440" cy="2160"/>
+          <a:ext cx="802080" cy="1800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6693,7 +6561,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>973800</xdr:colOff>
+      <xdr:colOff>973440</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>189360</xdr:rowOff>
     </xdr:to>
@@ -6705,7 +6573,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14126760" y="5894640"/>
-          <a:ext cx="745200" cy="360"/>
+          <a:ext cx="744840" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6741,7 +6609,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>872640</xdr:colOff>
+      <xdr:colOff>872280</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>118440</xdr:rowOff>
     </xdr:to>
@@ -6753,7 +6621,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13917240" y="2585160"/>
-          <a:ext cx="853560" cy="360"/>
+          <a:ext cx="853200" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6839,9 +6707,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>892080</xdr:colOff>
+      <xdr:colOff>891720</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>143280</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6851,7 +6719,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13905720" y="8631720"/>
-          <a:ext cx="884520" cy="74520"/>
+          <a:ext cx="884160" cy="74160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6887,9 +6755,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>828000</xdr:colOff>
+      <xdr:colOff>827640</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>143280</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6899,7 +6767,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14271480" y="8631720"/>
-          <a:ext cx="454680" cy="74520"/>
+          <a:ext cx="454320" cy="74160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6935,9 +6803,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>907560</xdr:colOff>
+      <xdr:colOff>907200</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>143280</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6947,7 +6815,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13921200" y="11298600"/>
-          <a:ext cx="884520" cy="74520"/>
+          <a:ext cx="884160" cy="74160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6983,9 +6851,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>881280</xdr:colOff>
+      <xdr:colOff>880920</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>143280</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6995,7 +6863,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14324760" y="11298600"/>
-          <a:ext cx="454680" cy="74520"/>
+          <a:ext cx="454320" cy="74160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7031,9 +6899,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>680400</xdr:colOff>
+      <xdr:colOff>680040</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>112320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7043,7 +6911,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13921200" y="11870280"/>
-          <a:ext cx="657360" cy="43920"/>
+          <a:ext cx="657000" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7079,9 +6947,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1011960</xdr:colOff>
+      <xdr:colOff>1011600</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>135360</xdr:rowOff>
+      <xdr:rowOff>135000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7091,7 +6959,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14667840" y="11892960"/>
-          <a:ext cx="242280" cy="43920"/>
+          <a:ext cx="241920" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7127,9 +6995,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1053720</xdr:colOff>
+      <xdr:colOff>1053360</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>135360</xdr:rowOff>
+      <xdr:rowOff>135000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7139,7 +7007,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14294520" y="11892960"/>
-          <a:ext cx="657360" cy="43920"/>
+          <a:ext cx="657000" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7175,7 +7043,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>672480</xdr:colOff>
+      <xdr:colOff>672120</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>106920</xdr:rowOff>
     </xdr:to>
@@ -7187,7 +7055,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13913280" y="12288960"/>
-          <a:ext cx="657360" cy="360"/>
+          <a:ext cx="657000" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7223,7 +7091,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1083960</xdr:colOff>
+      <xdr:colOff>1083600</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>106920</xdr:rowOff>
     </xdr:to>
@@ -7235,7 +7103,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14324760" y="12288960"/>
-          <a:ext cx="657360" cy="360"/>
+          <a:ext cx="657000" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7271,9 +7139,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1131480</xdr:colOff>
+      <xdr:colOff>1131120</xdr:colOff>
       <xdr:row>131</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>112320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7283,7 +7151,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14309640" y="25923240"/>
-          <a:ext cx="720000" cy="66960"/>
+          <a:ext cx="719640" cy="66600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7319,9 +7187,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>743040</xdr:colOff>
+      <xdr:colOff>742680</xdr:colOff>
       <xdr:row>131</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>112320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7331,7 +7199,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13921200" y="25923240"/>
-          <a:ext cx="720000" cy="66960"/>
+          <a:ext cx="719640" cy="66600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7367,9 +7235,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>717120</xdr:colOff>
+      <xdr:colOff>716760</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>112320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7379,7 +7247,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13936320" y="12990240"/>
-          <a:ext cx="678960" cy="66960"/>
+          <a:ext cx="678600" cy="66600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7415,9 +7283,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1059840</xdr:colOff>
+      <xdr:colOff>1059480</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>97560</xdr:rowOff>
+      <xdr:rowOff>97200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7427,7 +7295,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14279040" y="12975120"/>
-          <a:ext cx="678960" cy="66960"/>
+          <a:ext cx="678600" cy="66600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7463,9 +7331,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>702000</xdr:colOff>
+      <xdr:colOff>701640</xdr:colOff>
       <xdr:row>69</xdr:row>
-      <xdr:rowOff>105120</xdr:rowOff>
+      <xdr:rowOff>104760</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7475,7 +7343,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13921200" y="13935240"/>
-          <a:ext cx="678960" cy="66960"/>
+          <a:ext cx="678600" cy="66600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7511,9 +7379,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1113120</xdr:colOff>
+      <xdr:colOff>1112760</xdr:colOff>
       <xdr:row>69</xdr:row>
-      <xdr:rowOff>97560</xdr:rowOff>
+      <xdr:rowOff>97200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7523,7 +7391,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14332680" y="13927680"/>
-          <a:ext cx="678600" cy="66960"/>
+          <a:ext cx="678240" cy="66600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7559,7 +7427,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1065240</xdr:colOff>
+      <xdr:colOff>1064880</xdr:colOff>
       <xdr:row>69</xdr:row>
       <xdr:rowOff>84240</xdr:rowOff>
     </xdr:to>
@@ -7571,7 +7439,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14713560" y="13980960"/>
-          <a:ext cx="249840" cy="360"/>
+          <a:ext cx="249480" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7607,9 +7475,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>601200</xdr:colOff>
+      <xdr:colOff>600840</xdr:colOff>
       <xdr:row>130</xdr:row>
-      <xdr:rowOff>122040</xdr:rowOff>
+      <xdr:rowOff>121680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7619,7 +7487,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13937400" y="25745760"/>
-          <a:ext cx="561960" cy="63360"/>
+          <a:ext cx="561600" cy="63000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7655,9 +7523,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>929160</xdr:colOff>
+      <xdr:colOff>928800</xdr:colOff>
       <xdr:row>130</xdr:row>
-      <xdr:rowOff>131040</xdr:rowOff>
+      <xdr:rowOff>130680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7667,7 +7535,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14265360" y="25754760"/>
-          <a:ext cx="561960" cy="63360"/>
+          <a:ext cx="561600" cy="63000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7703,9 +7571,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>742320</xdr:colOff>
+      <xdr:colOff>741960</xdr:colOff>
       <xdr:row>120</xdr:row>
-      <xdr:rowOff>96120</xdr:rowOff>
+      <xdr:rowOff>95760</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7715,7 +7583,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13937400" y="23834160"/>
-          <a:ext cx="703080" cy="43920"/>
+          <a:ext cx="702720" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7751,9 +7619,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1122480</xdr:colOff>
+      <xdr:colOff>1122120</xdr:colOff>
       <xdr:row>120</xdr:row>
-      <xdr:rowOff>105120</xdr:rowOff>
+      <xdr:rowOff>104760</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7763,7 +7631,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14317560" y="23843160"/>
-          <a:ext cx="703080" cy="43920"/>
+          <a:ext cx="702720" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7799,7 +7667,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1052280</xdr:colOff>
+      <xdr:colOff>1051920</xdr:colOff>
       <xdr:row>120</xdr:row>
       <xdr:rowOff>87480</xdr:rowOff>
     </xdr:to>
@@ -7811,7 +7679,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14691600" y="23869080"/>
-          <a:ext cx="258840" cy="360"/>
+          <a:ext cx="258480" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7847,9 +7715,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>722880</xdr:colOff>
+      <xdr:colOff>722520</xdr:colOff>
       <xdr:row>119</xdr:row>
-      <xdr:rowOff>109080</xdr:rowOff>
+      <xdr:rowOff>108720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7861,7 +7729,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13917600" y="23643720"/>
-          <a:ext cx="703440" cy="56880"/>
+          <a:ext cx="703080" cy="56520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7897,9 +7765,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1070640</xdr:colOff>
+      <xdr:colOff>1070280</xdr:colOff>
       <xdr:row>129</xdr:row>
-      <xdr:rowOff>26640</xdr:rowOff>
+      <xdr:rowOff>26280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7909,7 +7777,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14265360" y="23764680"/>
-          <a:ext cx="703440" cy="1758600"/>
+          <a:ext cx="703080" cy="1758240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7945,9 +7813,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>788040</xdr:colOff>
+      <xdr:colOff>787680</xdr:colOff>
       <xdr:row>118</xdr:row>
-      <xdr:rowOff>128520</xdr:rowOff>
+      <xdr:rowOff>128160</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7957,7 +7825,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13930560" y="23485680"/>
-          <a:ext cx="755640" cy="43920"/>
+          <a:ext cx="755280" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7993,9 +7861,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1232280</xdr:colOff>
+      <xdr:colOff>1231920</xdr:colOff>
       <xdr:row>118</xdr:row>
-      <xdr:rowOff>109440</xdr:rowOff>
+      <xdr:rowOff>109080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8005,7 +7873,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14311080" y="23508720"/>
-          <a:ext cx="819360" cy="1800"/>
+          <a:ext cx="819000" cy="1440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8041,9 +7909,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>923040</xdr:colOff>
+      <xdr:colOff>922680</xdr:colOff>
       <xdr:row>113</xdr:row>
-      <xdr:rowOff>109080</xdr:rowOff>
+      <xdr:rowOff>108720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8053,7 +7921,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13924080" y="22513680"/>
-          <a:ext cx="897120" cy="43920"/>
+          <a:ext cx="896760" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8089,9 +7957,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>906480</xdr:colOff>
+      <xdr:colOff>906120</xdr:colOff>
       <xdr:row>113</xdr:row>
-      <xdr:rowOff>105120</xdr:rowOff>
+      <xdr:rowOff>104760</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8101,7 +7969,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14343480" y="22509720"/>
-          <a:ext cx="461160" cy="43920"/>
+          <a:ext cx="460800" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8137,9 +8005,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1202400</xdr:colOff>
+      <xdr:colOff>1202040</xdr:colOff>
       <xdr:row>113</xdr:row>
-      <xdr:rowOff>101160</xdr:rowOff>
+      <xdr:rowOff>100800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8149,7 +8017,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14769720" y="22505760"/>
-          <a:ext cx="330840" cy="43920"/>
+          <a:ext cx="330480" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8185,9 +8053,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>731160</xdr:colOff>
+      <xdr:colOff>730800</xdr:colOff>
       <xdr:row>111</xdr:row>
-      <xdr:rowOff>128520</xdr:rowOff>
+      <xdr:rowOff>128160</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8197,7 +8065,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13943880" y="22145760"/>
-          <a:ext cx="685440" cy="50400"/>
+          <a:ext cx="685080" cy="50040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8233,9 +8101,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1098720</xdr:colOff>
+      <xdr:colOff>1098360</xdr:colOff>
       <xdr:row>111</xdr:row>
-      <xdr:rowOff>124560</xdr:rowOff>
+      <xdr:rowOff>124200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8245,7 +8113,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14311080" y="22141800"/>
-          <a:ext cx="685800" cy="50400"/>
+          <a:ext cx="685440" cy="50040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8281,9 +8149,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1039680</xdr:colOff>
+      <xdr:colOff>1039320</xdr:colOff>
       <xdr:row>111</xdr:row>
-      <xdr:rowOff>120600</xdr:rowOff>
+      <xdr:rowOff>120240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8293,7 +8161,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14684760" y="22137840"/>
-          <a:ext cx="253080" cy="50400"/>
+          <a:ext cx="252720" cy="50040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8329,9 +8197,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>673200</xdr:colOff>
+      <xdr:colOff>672840</xdr:colOff>
       <xdr:row>104</xdr:row>
-      <xdr:rowOff>109080</xdr:rowOff>
+      <xdr:rowOff>108720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8341,7 +8209,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13956840" y="20799360"/>
-          <a:ext cx="614520" cy="43920"/>
+          <a:ext cx="614160" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8377,9 +8245,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1040400</xdr:colOff>
+      <xdr:colOff>1040040</xdr:colOff>
       <xdr:row>104</xdr:row>
-      <xdr:rowOff>111600</xdr:rowOff>
+      <xdr:rowOff>111240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8389,7 +8257,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14324040" y="20801880"/>
-          <a:ext cx="614520" cy="43920"/>
+          <a:ext cx="614160" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8425,9 +8293,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>746640</xdr:colOff>
+      <xdr:colOff>746280</xdr:colOff>
       <xdr:row>101</xdr:row>
-      <xdr:rowOff>89640</xdr:rowOff>
+      <xdr:rowOff>89280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8437,7 +8305,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13924080" y="20201760"/>
-          <a:ext cx="720720" cy="50400"/>
+          <a:ext cx="720360" cy="50040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8473,7 +8341,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1140120</xdr:colOff>
+      <xdr:colOff>1139760</xdr:colOff>
       <xdr:row>101</xdr:row>
       <xdr:rowOff>90360</xdr:rowOff>
     </xdr:to>
@@ -8485,7 +8353,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14317560" y="20252520"/>
-          <a:ext cx="720720" cy="360"/>
+          <a:ext cx="720360" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8521,9 +8389,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>695160</xdr:colOff>
+      <xdr:colOff>694800</xdr:colOff>
       <xdr:row>93</xdr:row>
-      <xdr:rowOff>122760</xdr:rowOff>
+      <xdr:rowOff>122400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8533,7 +8401,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13943880" y="18508320"/>
-          <a:ext cx="649440" cy="83520"/>
+          <a:ext cx="649080" cy="83160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8569,7 +8437,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1036080</xdr:colOff>
+      <xdr:colOff>1035720</xdr:colOff>
       <xdr:row>93</xdr:row>
       <xdr:rowOff>77400</xdr:rowOff>
     </xdr:to>
@@ -8581,7 +8449,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14695200" y="18546120"/>
-          <a:ext cx="239040" cy="360"/>
+          <a:ext cx="238680" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8617,7 +8485,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1177560</xdr:colOff>
+      <xdr:colOff>1177200</xdr:colOff>
       <xdr:row>93</xdr:row>
       <xdr:rowOff>63720</xdr:rowOff>
     </xdr:to>
@@ -8629,7 +8497,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14249880" y="18532440"/>
-          <a:ext cx="825840" cy="360"/>
+          <a:ext cx="825480" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8665,7 +8533,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>153000</xdr:colOff>
+      <xdr:colOff>152640</xdr:colOff>
       <xdr:row>93</xdr:row>
       <xdr:rowOff>88920</xdr:rowOff>
     </xdr:to>
@@ -8677,7 +8545,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="15146640" y="18557640"/>
-          <a:ext cx="153000" cy="360"/>
+          <a:ext cx="152640" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8713,7 +8581,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>153000</xdr:colOff>
+      <xdr:colOff>152640</xdr:colOff>
       <xdr:row>93</xdr:row>
       <xdr:rowOff>91800</xdr:rowOff>
     </xdr:to>
@@ -8725,7 +8593,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="15146640" y="18560520"/>
-          <a:ext cx="153000" cy="360"/>
+          <a:ext cx="152640" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8761,9 +8629,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>49320</xdr:colOff>
+      <xdr:colOff>48960</xdr:colOff>
       <xdr:row>93</xdr:row>
-      <xdr:rowOff>95760</xdr:rowOff>
+      <xdr:rowOff>95400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8773,7 +8641,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="15042960" y="18557640"/>
-          <a:ext cx="153000" cy="7200"/>
+          <a:ext cx="152640" cy="6840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8809,9 +8677,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>731160</xdr:colOff>
+      <xdr:colOff>730800</xdr:colOff>
       <xdr:row>92</xdr:row>
-      <xdr:rowOff>109080</xdr:rowOff>
+      <xdr:rowOff>108720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8821,7 +8689,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13943880" y="18343800"/>
-          <a:ext cx="685440" cy="43920"/>
+          <a:ext cx="685080" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8857,7 +8725,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1062360</xdr:colOff>
+      <xdr:colOff>1062000</xdr:colOff>
       <xdr:row>92</xdr:row>
       <xdr:rowOff>96840</xdr:rowOff>
     </xdr:to>
@@ -8869,7 +8737,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14708520" y="18375120"/>
-          <a:ext cx="252000" cy="360"/>
+          <a:ext cx="251640" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8905,9 +8773,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1050480</xdr:colOff>
+      <xdr:colOff>1050120</xdr:colOff>
       <xdr:row>92</xdr:row>
-      <xdr:rowOff>126000</xdr:rowOff>
+      <xdr:rowOff>125640</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8917,7 +8785,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14262840" y="18360720"/>
-          <a:ext cx="685800" cy="43920"/>
+          <a:ext cx="685440" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8953,9 +8821,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>729000</xdr:colOff>
+      <xdr:colOff>728640</xdr:colOff>
       <xdr:row>82</xdr:row>
-      <xdr:rowOff>115560</xdr:rowOff>
+      <xdr:rowOff>115200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8965,7 +8833,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13924080" y="16445160"/>
-          <a:ext cx="703080" cy="43920"/>
+          <a:ext cx="702720" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9001,9 +8869,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1096560</xdr:colOff>
+      <xdr:colOff>1096200</xdr:colOff>
       <xdr:row>82</xdr:row>
-      <xdr:rowOff>118080</xdr:rowOff>
+      <xdr:rowOff>117720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9013,7 +8881,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14291640" y="16447680"/>
-          <a:ext cx="703080" cy="43920"/>
+          <a:ext cx="702720" cy="43560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9049,9 +8917,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>987840</xdr:colOff>
+      <xdr:colOff>987480</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:rowOff>165960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9061,7 +8929,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13940280" y="2346840"/>
-          <a:ext cx="945720" cy="96120"/>
+          <a:ext cx="945360" cy="95760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9097,9 +8965,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>954000</xdr:colOff>
+      <xdr:colOff>953640</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>152280</xdr:rowOff>
+      <xdr:rowOff>151920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9109,7 +8977,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14346360" y="2346840"/>
-          <a:ext cx="505800" cy="82080"/>
+          <a:ext cx="505440" cy="81720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9145,9 +9013,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>817560</xdr:colOff>
+      <xdr:colOff>817200</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>112320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9157,7 +9025,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13913280" y="6768360"/>
-          <a:ext cx="802440" cy="2160"/>
+          <a:ext cx="802080" cy="1800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9193,7 +9061,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>973800</xdr:colOff>
+      <xdr:colOff>973440</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>189360</xdr:rowOff>
     </xdr:to>
@@ -9205,7 +9073,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14126760" y="6846840"/>
-          <a:ext cx="745200" cy="360"/>
+          <a:ext cx="744840" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9241,9 +9109,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>817560</xdr:colOff>
+      <xdr:colOff>817200</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>112320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9253,7 +9121,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13913280" y="7911360"/>
-          <a:ext cx="802440" cy="2160"/>
+          <a:ext cx="802080" cy="1800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9289,7 +9157,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>973800</xdr:colOff>
+      <xdr:colOff>973440</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>189360</xdr:rowOff>
     </xdr:to>
@@ -9301,7 +9169,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14126760" y="7989840"/>
-          <a:ext cx="745200" cy="360"/>
+          <a:ext cx="744840" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9337,9 +9205,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>817560</xdr:colOff>
+      <xdr:colOff>817200</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>112320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9349,7 +9217,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13913280" y="10197360"/>
-          <a:ext cx="802440" cy="2160"/>
+          <a:ext cx="802080" cy="1800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9385,7 +9253,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>973800</xdr:colOff>
+      <xdr:colOff>973440</xdr:colOff>
       <xdr:row>49</xdr:row>
       <xdr:rowOff>189360</xdr:rowOff>
     </xdr:to>
@@ -9397,7 +9265,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14126760" y="10275840"/>
-          <a:ext cx="745200" cy="360"/>
+          <a:ext cx="744840" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9433,9 +9301,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>817560</xdr:colOff>
+      <xdr:colOff>817200</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>112320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9445,7 +9313,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13913280" y="9626040"/>
-          <a:ext cx="802440" cy="2160"/>
+          <a:ext cx="802080" cy="1800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9481,7 +9349,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>973800</xdr:colOff>
+      <xdr:colOff>973440</xdr:colOff>
       <xdr:row>46</xdr:row>
       <xdr:rowOff>189360</xdr:rowOff>
     </xdr:to>
@@ -9493,7 +9361,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14126760" y="9704520"/>
-          <a:ext cx="745200" cy="360"/>
+          <a:ext cx="744840" cy="360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9529,9 +9397,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1058760</xdr:colOff>
+      <xdr:colOff>1058400</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:rowOff>165960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9541,7 +9409,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13898160" y="5775840"/>
-          <a:ext cx="1058760" cy="96120"/>
+          <a:ext cx="1058400" cy="95760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9577,9 +9445,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>977400</xdr:colOff>
+      <xdr:colOff>977040</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>164520</xdr:rowOff>
+      <xdr:rowOff>164160</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9589,7 +9457,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14330880" y="5774040"/>
-          <a:ext cx="544680" cy="96120"/>
+          <a:ext cx="544320" cy="95760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9625,9 +9493,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1110960</xdr:colOff>
+      <xdr:colOff>1110600</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>138240</xdr:rowOff>
+      <xdr:rowOff>137880</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9637,7 +9505,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13912200" y="6714000"/>
-          <a:ext cx="1096920" cy="82080"/>
+          <a:ext cx="1096560" cy="81720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9673,9 +9541,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1010520</xdr:colOff>
+      <xdr:colOff>1010160</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>150480</xdr:rowOff>
+      <xdr:rowOff>150120</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9685,7 +9553,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14344560" y="6726240"/>
-          <a:ext cx="564120" cy="82080"/>
+          <a:ext cx="563760" cy="81720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9721,9 +9589,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>950040</xdr:colOff>
+      <xdr:colOff>949680</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>138600</xdr:rowOff>
+      <xdr:rowOff>138240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9733,7 +9601,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13940280" y="7871040"/>
-          <a:ext cx="907920" cy="68400"/>
+          <a:ext cx="907560" cy="68040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9769,9 +9637,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>955440</xdr:colOff>
+      <xdr:colOff>955080</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>136800</xdr:rowOff>
+      <xdr:rowOff>136440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9781,7 +9649,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14386680" y="7869240"/>
-          <a:ext cx="466920" cy="68400"/>
+          <a:ext cx="466560" cy="68040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9817,9 +9685,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>946440</xdr:colOff>
+      <xdr:colOff>946080</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>149040</xdr:rowOff>
+      <xdr:rowOff>148680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9829,7 +9697,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13936680" y="9596160"/>
-          <a:ext cx="907920" cy="68400"/>
+          <a:ext cx="907560" cy="68040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9865,9 +9733,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>952200</xdr:colOff>
+      <xdr:colOff>951840</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>161280</xdr:rowOff>
+      <xdr:rowOff>160920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9877,7 +9745,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14383440" y="9608400"/>
-          <a:ext cx="466920" cy="68400"/>
+          <a:ext cx="466560" cy="68040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9913,9 +9781,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1237320</xdr:colOff>
+      <xdr:colOff>1236960</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>145800</xdr:rowOff>
+      <xdr:rowOff>145440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9925,7 +9793,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14801760" y="9592920"/>
-          <a:ext cx="333720" cy="68400"/>
+          <a:ext cx="333360" cy="68040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9961,9 +9829,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>964080</xdr:colOff>
+      <xdr:colOff>963720</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>152280</xdr:rowOff>
+      <xdr:rowOff>151920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9973,7 +9841,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="13954320" y="10170720"/>
-          <a:ext cx="907920" cy="68400"/>
+          <a:ext cx="907560" cy="68040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10009,9 +9877,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>941400</xdr:colOff>
+      <xdr:colOff>941040</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>136800</xdr:rowOff>
+      <xdr:rowOff>136440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -10021,7 +9889,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14372640" y="10155240"/>
-          <a:ext cx="466920" cy="68400"/>
+          <a:ext cx="466560" cy="68040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -32922,6 +32790,12 @@
         <v>90</v>
       </c>
       <c r="E139" s="33"/>
+      <c r="G139" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="H139" s="32" t="s">
+        <v>90</v>
+      </c>
       <c r="I139" s="40"/>
       <c r="K139" s="36" t="s">
         <v>90</v>
@@ -32940,6 +32814,12 @@
       <c r="C140" s="33" t="s">
         <v>90</v>
       </c>
+      <c r="G140" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="H140" s="32" t="s">
+        <v>90</v>
+      </c>
       <c r="K140" s="36" t="s">
         <v>90</v>
       </c>
@@ -32957,6 +32837,12 @@
       <c r="C141" s="33" t="s">
         <v>90</v>
       </c>
+      <c r="G141" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="H141" s="32" t="s">
+        <v>90</v>
+      </c>
       <c r="K141" s="36" t="s">
         <v>90</v>
       </c>
@@ -32974,6 +32860,12 @@
       <c r="C142" s="33" t="s">
         <v>90</v>
       </c>
+      <c r="G142" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="H142" s="32" t="s">
+        <v>90</v>
+      </c>
       <c r="K142" s="36" t="s">
         <v>90</v>
       </c>
@@ -32991,6 +32883,12 @@
       <c r="C143" s="33" t="s">
         <v>90</v>
       </c>
+      <c r="G143" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="H143" s="32" t="s">
+        <v>90</v>
+      </c>
       <c r="K143" s="36" t="s">
         <v>90</v>
       </c>
@@ -33008,6 +32906,12 @@
       <c r="C144" s="33" t="s">
         <v>90</v>
       </c>
+      <c r="G144" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="H144" s="32" t="s">
+        <v>90</v>
+      </c>
       <c r="K144" s="36" t="s">
         <v>90</v>
       </c>
@@ -33023,6 +32927,12 @@
         <v>419</v>
       </c>
       <c r="C145" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="G145" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="H145" s="32" t="s">
         <v>90</v>
       </c>
       <c r="K145" s="36" t="s">
